--- a/School_Mang/EXCEL/Final/Term_B/Term_B_2.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_2.xlsx
@@ -518,7 +518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:O152"/>
+  <dimension ref="A2:AD152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="8"/>
@@ -532,7 +532,7 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
         <v>12</v>
       </c>
@@ -547,7 +547,7 @@
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="2"/>
@@ -562,7 +562,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -603,7 +603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="5"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="M5" s="11"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="5"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="5"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="M7" s="11"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="5"/>
@@ -726,8 +726,12 @@
         <v>0</v>
       </c>
       <c r="M8" s="11"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AD8" s="1">
+        <f>SUM(E5:L20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="5"/>
@@ -758,7 +762,7 @@
       </c>
       <c r="M9" s="12"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="5"/>
@@ -789,7 +793,7 @@
       </c>
       <c r="M10" s="12"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="5"/>
@@ -820,7 +824,7 @@
       </c>
       <c r="M11" s="12"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="5"/>
@@ -851,7 +855,7 @@
       </c>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="5"/>
@@ -882,7 +886,7 @@
       </c>
       <c r="M13" s="12"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="5"/>
@@ -913,7 +917,7 @@
       </c>
       <c r="M14" s="12"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="5"/>
@@ -944,7 +948,7 @@
       </c>
       <c r="M15" s="12"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="5"/>

--- a/School_Mang/EXCEL/Final/Term_B/Term_B_2.xlsx
+++ b/School_Mang/EXCEL/Final/Term_B/Term_B_2.xlsx
@@ -183,7 +183,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF8B8B"/>
+          <bgColor rgb="FFFADF53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC5C5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5201,16 +5223,16 @@
     <mergeCell ref="B2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:M152">
-    <cfRule type="containsBlanks" dxfId="2" priority="3">
+    <cfRule type="containsBlanks" dxfId="5" priority="3">
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:L152">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="greaterThan">
-      <formula>70</formula>
+    <cfRule type="cellIs" dxfId="3" priority="20" operator="greaterThan">
+      <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
